--- a/notebooks/Random Forest/predictions_ele_2025.xlsx
+++ b/notebooks/Random Forest/predictions_ele_2025.xlsx
@@ -463,7 +463,7 @@
         <v>70.06791937865498</v>
       </c>
       <c r="D2" t="n">
-        <v>69.76901444225484</v>
+        <v>69.76901444225483</v>
       </c>
     </row>
     <row r="3">
@@ -476,7 +476,7 @@
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>68.08643038600285</v>
+        <v>68.08643038600289</v>
       </c>
       <c r="D3" t="n">
         <v>67.8793325595238</v>
@@ -492,10 +492,10 @@
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>70.54224977633478</v>
+        <v>70.5422497763348</v>
       </c>
       <c r="D4" t="n">
-        <v>69.95633003968256</v>
+        <v>69.95633003968254</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>71.39897614718616</v>
+        <v>71.39897614718615</v>
       </c>
       <c r="D5" t="n">
-        <v>70.57824481962484</v>
+        <v>70.57824481962486</v>
       </c>
     </row>
     <row r="6">
@@ -543,7 +543,7 @@
         <v>70.92661077741707</v>
       </c>
       <c r="D7" t="n">
-        <v>70.3362474738931</v>
+        <v>70.33624747389308</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>70.56354864538238</v>
+        <v>70.56354864538241</v>
       </c>
       <c r="D8" t="n">
         <v>70.01620869769118</v>
@@ -575,7 +575,7 @@
         <v>72.99912950396822</v>
       </c>
       <c r="D9" t="n">
-        <v>72.22473489163613</v>
+        <v>72.22473489163612</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         <v>70.60835704184707</v>
       </c>
       <c r="D10" t="n">
-        <v>70.07619990800868</v>
+        <v>70.07619990800866</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>72.13483005673247</v>
+        <v>72.1348300567325</v>
       </c>
       <c r="D11" t="n">
         <v>71.18796832611838</v>
@@ -620,10 +620,10 @@
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>68.50094651695525</v>
+        <v>68.50094651695528</v>
       </c>
       <c r="D12" t="n">
-        <v>68.58014690836941</v>
+        <v>68.5801469083694</v>
       </c>
     </row>
     <row r="13">
@@ -636,7 +636,7 @@
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>72.70783295634919</v>
+        <v>72.70783295634918</v>
       </c>
       <c r="D13" t="n">
         <v>72.10354820067185</v>
@@ -652,10 +652,10 @@
         <v>2025</v>
       </c>
       <c r="C14" t="n">
-        <v>70.28152107142859</v>
+        <v>70.28152107142861</v>
       </c>
       <c r="D14" t="n">
-        <v>69.83315131464413</v>
+        <v>69.83315131464414</v>
       </c>
     </row>
     <row r="15">
@@ -668,7 +668,7 @@
         <v>2025</v>
       </c>
       <c r="C15" t="n">
-        <v>69.7810808488764</v>
+        <v>69.78108084887639</v>
       </c>
       <c r="D15" t="n">
         <v>69.60924768462407</v>
@@ -684,10 +684,10 @@
         <v>2025</v>
       </c>
       <c r="C16" t="n">
-        <v>76.97517753968253</v>
+        <v>76.97517753968251</v>
       </c>
       <c r="D16" t="n">
-        <v>76.65837158369409</v>
+        <v>76.65837158369411</v>
       </c>
     </row>
     <row r="17">
@@ -719,7 +719,7 @@
         <v>72.3660474801587</v>
       </c>
       <c r="D18" t="n">
-        <v>71.70115386904767</v>
+        <v>71.70115386904766</v>
       </c>
     </row>
     <row r="19">
@@ -732,10 +732,10 @@
         <v>2025</v>
       </c>
       <c r="C19" t="n">
-        <v>69.9692292216117</v>
+        <v>69.96922922161167</v>
       </c>
       <c r="D19" t="n">
-        <v>69.77425182720054</v>
+        <v>69.77425182720053</v>
       </c>
     </row>
     <row r="20">
@@ -748,10 +748,10 @@
         <v>2025</v>
       </c>
       <c r="C20" t="n">
-        <v>76.24578879731381</v>
+        <v>76.24578879731382</v>
       </c>
       <c r="D20" t="n">
-        <v>76.30262157661785</v>
+        <v>76.30262157661787</v>
       </c>
     </row>
     <row r="21">
@@ -764,10 +764,10 @@
         <v>2025</v>
       </c>
       <c r="C21" t="n">
-        <v>69.87332084184986</v>
+        <v>69.87332084184985</v>
       </c>
       <c r="D21" t="n">
-        <v>69.82985179012876</v>
+        <v>69.82985179012873</v>
       </c>
     </row>
     <row r="22">
@@ -780,7 +780,7 @@
         <v>2025</v>
       </c>
       <c r="C22" t="n">
-        <v>70.91499133297263</v>
+        <v>70.91499133297265</v>
       </c>
       <c r="D22" t="n">
         <v>70.2746342992899</v>
@@ -815,7 +815,7 @@
         <v>73.00384263888887</v>
       </c>
       <c r="D24" t="n">
-        <v>72.24650476190475</v>
+        <v>72.24650476190473</v>
       </c>
     </row>
     <row r="25">
@@ -828,10 +828,10 @@
         <v>2025</v>
       </c>
       <c r="C25" t="n">
-        <v>70.34366051046177</v>
+        <v>70.3436605104618</v>
       </c>
       <c r="D25" t="n">
-        <v>69.87667739775804</v>
+        <v>69.87667739775806</v>
       </c>
     </row>
     <row r="26">
@@ -844,7 +844,7 @@
         <v>2025</v>
       </c>
       <c r="C26" t="n">
-        <v>69.57516104653682</v>
+        <v>69.57516104653679</v>
       </c>
       <c r="D26" t="n">
         <v>69.34763910894664</v>
@@ -876,7 +876,7 @@
         <v>2025</v>
       </c>
       <c r="C28" t="n">
-        <v>74.7669846780996</v>
+        <v>74.76698467809962</v>
       </c>
       <c r="D28" t="n">
         <v>74.51587798701291</v>
@@ -911,7 +911,7 @@
         <v>68.80912606782108</v>
       </c>
       <c r="D30" t="n">
-        <v>68.67129505591629</v>
+        <v>68.67129505591627</v>
       </c>
     </row>
     <row r="31">
@@ -924,10 +924,10 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>74.38166690566374</v>
+        <v>74.38166690566372</v>
       </c>
       <c r="D31" t="n">
-        <v>74.38604609217167</v>
+        <v>74.38604609217164</v>
       </c>
     </row>
     <row r="32">
@@ -940,7 +940,7 @@
         <v>2025</v>
       </c>
       <c r="C32" t="n">
-        <v>69.96380410256408</v>
+        <v>69.96380410256407</v>
       </c>
       <c r="D32" t="n">
         <v>69.79870509620977</v>
@@ -959,7 +959,7 @@
         <v>69.95911630494503</v>
       </c>
       <c r="D33" t="n">
-        <v>69.64170533910533</v>
+        <v>69.64170533910529</v>
       </c>
     </row>
     <row r="34">
@@ -972,10 +972,10 @@
         <v>2025</v>
       </c>
       <c r="C34" t="n">
-        <v>70.99946946428575</v>
+        <v>70.99946946428577</v>
       </c>
       <c r="D34" t="n">
-        <v>70.25772639524949</v>
+        <v>70.25772639524951</v>
       </c>
     </row>
     <row r="35">
@@ -988,10 +988,10 @@
         <v>2025</v>
       </c>
       <c r="C35" t="n">
-        <v>69.93313459859583</v>
+        <v>69.93313459859581</v>
       </c>
       <c r="D35" t="n">
-        <v>69.71034023529465</v>
+        <v>69.71034023529462</v>
       </c>
     </row>
     <row r="36">
@@ -1004,7 +1004,7 @@
         <v>2025</v>
       </c>
       <c r="C36" t="n">
-        <v>71.40979787698417</v>
+        <v>71.40979787698419</v>
       </c>
       <c r="D36" t="n">
         <v>70.57356456168831</v>
@@ -1036,10 +1036,10 @@
         <v>2025</v>
       </c>
       <c r="C38" t="n">
-        <v>70.33327114452797</v>
+        <v>70.333271144528</v>
       </c>
       <c r="D38" t="n">
-        <v>69.87321250692406</v>
+        <v>69.87321250692405</v>
       </c>
     </row>
     <row r="39">
@@ -1052,7 +1052,7 @@
         <v>2025</v>
       </c>
       <c r="C39" t="n">
-        <v>70.53366755411257</v>
+        <v>70.5336675541126</v>
       </c>
       <c r="D39" t="n">
         <v>69.96263849206349</v>
@@ -1068,7 +1068,7 @@
         <v>2025</v>
       </c>
       <c r="C40" t="n">
-        <v>71.993973602244</v>
+        <v>71.99397360224398</v>
       </c>
       <c r="D40" t="n">
         <v>70.99060229617609</v>
@@ -1084,7 +1084,7 @@
         <v>2025</v>
       </c>
       <c r="C41" t="n">
-        <v>70.18138142230578</v>
+        <v>70.18138142230579</v>
       </c>
       <c r="D41" t="n">
         <v>69.72591703243124</v>
@@ -1103,7 +1103,7 @@
         <v>69.90624534181097</v>
       </c>
       <c r="D42" t="n">
-        <v>69.84249822601009</v>
+        <v>69.84249822601008</v>
       </c>
     </row>
     <row r="43">
@@ -1116,10 +1116,10 @@
         <v>2025</v>
       </c>
       <c r="C43" t="n">
-        <v>69.83554622255782</v>
+        <v>69.83554622255784</v>
       </c>
       <c r="D43" t="n">
-        <v>69.79331524250966</v>
+        <v>69.79331524250965</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         <v>75.39947589133078</v>
       </c>
       <c r="D44" t="n">
-        <v>75.40469124847365</v>
+        <v>75.40469124847364</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         <v>68.9933350757576</v>
       </c>
       <c r="D45" t="n">
-        <v>68.70651573967702</v>
+        <v>68.70651573967699</v>
       </c>
     </row>
     <row r="46">
@@ -1164,7 +1164,7 @@
         <v>2025</v>
       </c>
       <c r="C46" t="n">
-        <v>72.62738982142854</v>
+        <v>72.62738982142857</v>
       </c>
       <c r="D46" t="n">
         <v>72.13781418319083</v>
@@ -1183,7 +1183,7 @@
         <v>69.29835877831107</v>
       </c>
       <c r="D47" t="n">
-        <v>68.75771569083696</v>
+        <v>68.75771569083695</v>
       </c>
     </row>
     <row r="48">
@@ -1212,7 +1212,7 @@
         <v>2025</v>
       </c>
       <c r="C49" t="n">
-        <v>78.47247692460317</v>
+        <v>78.47247692460316</v>
       </c>
       <c r="D49" t="n">
         <v>77.99106084776332</v>
@@ -1231,7 +1231,7 @@
         <v>74.39055444444442</v>
       </c>
       <c r="D50" t="n">
-        <v>74.36318464285711</v>
+        <v>74.36318464285709</v>
       </c>
     </row>
     <row r="51">
@@ -1244,10 +1244,10 @@
         <v>2025</v>
       </c>
       <c r="C51" t="n">
-        <v>69.48407611549874</v>
+        <v>69.48407611549875</v>
       </c>
       <c r="D51" t="n">
-        <v>69.12575218692733</v>
+        <v>69.12575218692734</v>
       </c>
     </row>
     <row r="52">
@@ -1260,10 +1260,10 @@
         <v>2025</v>
       </c>
       <c r="C52" t="n">
-        <v>69.96897201923075</v>
+        <v>69.96897201923073</v>
       </c>
       <c r="D52" t="n">
-        <v>69.76810174541085</v>
+        <v>69.76810174541082</v>
       </c>
     </row>
     <row r="53">
@@ -1276,10 +1276,10 @@
         <v>2025</v>
       </c>
       <c r="C53" t="n">
-        <v>72.01289339120503</v>
+        <v>72.01289339120504</v>
       </c>
       <c r="D53" t="n">
-        <v>71.04471855519486</v>
+        <v>71.04471855519488</v>
       </c>
     </row>
     <row r="54">
@@ -1292,7 +1292,7 @@
         <v>2025</v>
       </c>
       <c r="C54" t="n">
-        <v>70.95979224567105</v>
+        <v>70.95979224567104</v>
       </c>
       <c r="D54" t="n">
         <v>70.25416180194807</v>
@@ -1308,7 +1308,7 @@
         <v>2025</v>
       </c>
       <c r="C55" t="n">
-        <v>73.29899968253967</v>
+        <v>73.29899968253966</v>
       </c>
       <c r="D55" t="n">
         <v>72.58414547619046</v>
@@ -1324,10 +1324,10 @@
         <v>2025</v>
       </c>
       <c r="C56" t="n">
-        <v>67.27215010461755</v>
+        <v>67.27215010461757</v>
       </c>
       <c r="D56" t="n">
-        <v>67.60832706890326</v>
+        <v>67.60832706890329</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         <v>76.05781855921855</v>
       </c>
       <c r="D57" t="n">
-        <v>76.25482711233211</v>
+        <v>76.25482711233212</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1359,7 @@
         <v>74.67610972943714</v>
       </c>
       <c r="D58" t="n">
-        <v>74.4528658441558</v>
+        <v>74.45286584415578</v>
       </c>
     </row>
     <row r="59">
@@ -1372,7 +1372,7 @@
         <v>2025</v>
       </c>
       <c r="C59" t="n">
-        <v>66.80938938492059</v>
+        <v>66.80938938492062</v>
       </c>
       <c r="D59" t="n">
         <v>66.8130793849206</v>
@@ -1391,7 +1391,7 @@
         <v>70.0357409550172</v>
       </c>
       <c r="D60" t="n">
-        <v>69.90943861921454</v>
+        <v>69.90943861921455</v>
       </c>
     </row>
     <row r="61">
@@ -1420,10 +1420,10 @@
         <v>2025</v>
       </c>
       <c r="C62" t="n">
-        <v>72.59319849206345</v>
+        <v>72.59319849206349</v>
       </c>
       <c r="D62" t="n">
-        <v>72.105120540461</v>
+        <v>72.10512054046099</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1439,7 @@
         <v>71.96652597057013</v>
       </c>
       <c r="D63" t="n">
-        <v>71.0201172889611</v>
+        <v>71.02011728896109</v>
       </c>
     </row>
     <row r="64">
@@ -1452,10 +1452,10 @@
         <v>2025</v>
       </c>
       <c r="C64" t="n">
-        <v>72.68535815476187</v>
+        <v>72.6853581547619</v>
       </c>
       <c r="D64" t="n">
-        <v>72.13486138557181</v>
+        <v>72.1348613855718</v>
       </c>
     </row>
     <row r="65">
@@ -1484,7 +1484,7 @@
         <v>2025</v>
       </c>
       <c r="C66" t="n">
-        <v>70.85037538059164</v>
+        <v>70.85037538059166</v>
       </c>
       <c r="D66" t="n">
         <v>70.21275078738513</v>
@@ -1500,7 +1500,7 @@
         <v>2025</v>
       </c>
       <c r="C67" t="n">
-        <v>70.52399041125544</v>
+        <v>70.52399041125547</v>
       </c>
       <c r="D67" t="n">
         <v>69.94827218253967</v>
@@ -1516,7 +1516,7 @@
         <v>2025</v>
       </c>
       <c r="C68" t="n">
-        <v>74.85829465825836</v>
+        <v>74.85829465825837</v>
       </c>
       <c r="D68" t="n">
         <v>74.6011018362193</v>
@@ -1532,10 +1532,10 @@
         <v>2025</v>
       </c>
       <c r="C69" t="n">
-        <v>72.02003355173895</v>
+        <v>72.02003355173893</v>
       </c>
       <c r="D69" t="n">
-        <v>70.98576974567106</v>
+        <v>70.98576974567105</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1551,7 @@
         <v>69.98605899614273</v>
       </c>
       <c r="D70" t="n">
-        <v>69.74899194192488</v>
+        <v>69.74899194192486</v>
       </c>
     </row>
     <row r="71">
@@ -1580,10 +1580,10 @@
         <v>2025</v>
       </c>
       <c r="C72" t="n">
-        <v>71.35189353535355</v>
+        <v>71.35189353535357</v>
       </c>
       <c r="D72" t="n">
-        <v>70.54585668831169</v>
+        <v>70.54585668831167</v>
       </c>
     </row>
     <row r="73">
@@ -1596,10 +1596,10 @@
         <v>2025</v>
       </c>
       <c r="C73" t="n">
-        <v>75.51926762112878</v>
+        <v>75.51926762112876</v>
       </c>
       <c r="D73" t="n">
-        <v>75.56841815684305</v>
+        <v>75.56841815684304</v>
       </c>
     </row>
     <row r="74">
@@ -1612,10 +1612,10 @@
         <v>2025</v>
       </c>
       <c r="C74" t="n">
-        <v>71.63286970238097</v>
+        <v>71.63286970238099</v>
       </c>
       <c r="D74" t="n">
-        <v>70.69388798881674</v>
+        <v>70.69388798881675</v>
       </c>
     </row>
     <row r="75">
@@ -1628,7 +1628,7 @@
         <v>2025</v>
       </c>
       <c r="C75" t="n">
-        <v>70.93667387265515</v>
+        <v>70.93667387265518</v>
       </c>
       <c r="D75" t="n">
         <v>70.3445290377459</v>
@@ -1647,7 +1647,7 @@
         <v>69.85965619548011</v>
       </c>
       <c r="D76" t="n">
-        <v>69.79240632124819</v>
+        <v>69.79240632124818</v>
       </c>
     </row>
     <row r="77">
@@ -1660,10 +1660,10 @@
         <v>2025</v>
       </c>
       <c r="C77" t="n">
-        <v>76.32901453144078</v>
+        <v>76.32901453144081</v>
       </c>
       <c r="D77" t="n">
-        <v>76.38702237026864</v>
+        <v>76.38702237026865</v>
       </c>
     </row>
     <row r="78">
@@ -1676,7 +1676,7 @@
         <v>2025</v>
       </c>
       <c r="C78" t="n">
-        <v>71.87497668109668</v>
+        <v>71.8749766810967</v>
       </c>
       <c r="D78" t="n">
         <v>70.96028886544015</v>
@@ -1695,7 +1695,7 @@
         <v>76.20309568223445</v>
       </c>
       <c r="D79" t="n">
-        <v>76.4439930647131</v>
+        <v>76.44399306471313</v>
       </c>
     </row>
     <row r="80">
@@ -1708,7 +1708,7 @@
         <v>2025</v>
       </c>
       <c r="C80" t="n">
-        <v>72.31398700396822</v>
+        <v>72.31398700396824</v>
       </c>
       <c r="D80" t="n">
         <v>71.63002021464651</v>
@@ -1727,7 +1727,7 @@
         <v>65.7572507593795</v>
       </c>
       <c r="D81" t="n">
-        <v>65.65254819985572</v>
+        <v>65.65254819985569</v>
       </c>
     </row>
     <row r="82">
@@ -1759,7 +1759,7 @@
         <v>70.94265561868693</v>
       </c>
       <c r="D83" t="n">
-        <v>70.31398035087722</v>
+        <v>70.3139803508772</v>
       </c>
     </row>
     <row r="84">
@@ -1772,10 +1772,10 @@
         <v>2025</v>
       </c>
       <c r="C84" t="n">
-        <v>78.22840503968251</v>
+        <v>78.2284050396825</v>
       </c>
       <c r="D84" t="n">
-        <v>77.79583051046171</v>
+        <v>77.7958305104617</v>
       </c>
     </row>
     <row r="85">
@@ -1788,7 +1788,7 @@
         <v>2025</v>
       </c>
       <c r="C85" t="n">
-        <v>76.49568935078811</v>
+        <v>76.49568935078813</v>
       </c>
       <c r="D85" t="n">
         <v>76.54419351745479</v>
@@ -1804,7 +1804,7 @@
         <v>2025</v>
       </c>
       <c r="C86" t="n">
-        <v>76.02851451159951</v>
+        <v>76.02851451159952</v>
       </c>
       <c r="D86" t="n">
         <v>76.2348195131258</v>

--- a/notebooks/Random Forest/predictions_ele_2025.xlsx
+++ b/notebooks/Random Forest/predictions_ele_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ОПЖ</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>predictions</t>
+          <t>ОПЖ_прогноз</t>
         </is>
       </c>
     </row>
@@ -460,10 +455,7 @@
         <v>2025</v>
       </c>
       <c r="C2" t="n">
-        <v>70.06791937865498</v>
-      </c>
-      <c r="D2" t="n">
-        <v>69.76901444225483</v>
+        <v>69.61282737347946</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +468,7 @@
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>68.08643038600289</v>
-      </c>
-      <c r="D3" t="n">
-        <v>67.8793325595238</v>
+        <v>67.88796251984124</v>
       </c>
     </row>
     <row r="4">
@@ -492,10 +481,7 @@
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>70.5422497763348</v>
-      </c>
-      <c r="D4" t="n">
-        <v>69.95633003968254</v>
+        <v>70.15226491526761</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +494,7 @@
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>71.39897614718615</v>
-      </c>
-      <c r="D5" t="n">
-        <v>70.57824481962486</v>
+        <v>71.23793286160405</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +507,7 @@
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>72.96664805555554</v>
-      </c>
-      <c r="D6" t="n">
-        <v>72.21044999999995</v>
+        <v>72.33046153541459</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +520,7 @@
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>70.92661077741707</v>
-      </c>
-      <c r="D7" t="n">
-        <v>70.33624747389308</v>
+        <v>70.64335969244267</v>
       </c>
     </row>
     <row r="8">
@@ -556,10 +533,7 @@
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>70.56354864538241</v>
-      </c>
-      <c r="D8" t="n">
-        <v>70.01620869769118</v>
+        <v>70.26756387667584</v>
       </c>
     </row>
     <row r="9">
@@ -572,10 +546,7 @@
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>72.99912950396822</v>
-      </c>
-      <c r="D9" t="n">
-        <v>72.22473489163612</v>
+        <v>72.19887734028204</v>
       </c>
     </row>
     <row r="10">
@@ -588,10 +559,7 @@
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>70.60835704184707</v>
-      </c>
-      <c r="D10" t="n">
-        <v>70.07619990800866</v>
+        <v>70.48455934072689</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +572,7 @@
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>72.1348300567325</v>
-      </c>
-      <c r="D11" t="n">
-        <v>71.18796832611838</v>
+        <v>71.53173902849305</v>
       </c>
     </row>
     <row r="12">
@@ -620,10 +585,7 @@
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>68.50094651695528</v>
-      </c>
-      <c r="D12" t="n">
-        <v>68.5801469083694</v>
+        <v>68.02671882034635</v>
       </c>
     </row>
     <row r="13">
@@ -636,10 +598,7 @@
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>72.70783295634918</v>
-      </c>
-      <c r="D13" t="n">
-        <v>72.10354820067185</v>
+        <v>72.03519136603481</v>
       </c>
     </row>
     <row r="14">
@@ -652,10 +611,7 @@
         <v>2025</v>
       </c>
       <c r="C14" t="n">
-        <v>70.28152107142861</v>
-      </c>
-      <c r="D14" t="n">
-        <v>69.83315131464414</v>
+        <v>69.7529843093905</v>
       </c>
     </row>
     <row r="15">
@@ -668,10 +624,7 @@
         <v>2025</v>
       </c>
       <c r="C15" t="n">
-        <v>69.78108084887639</v>
-      </c>
-      <c r="D15" t="n">
-        <v>69.60924768462407</v>
+        <v>68.87771785696492</v>
       </c>
     </row>
     <row r="16">
@@ -684,10 +637,7 @@
         <v>2025</v>
       </c>
       <c r="C16" t="n">
-        <v>76.97517753968251</v>
-      </c>
-      <c r="D16" t="n">
-        <v>76.65837158369411</v>
+        <v>74.70453910466946</v>
       </c>
     </row>
     <row r="17">
@@ -700,10 +650,7 @@
         <v>2025</v>
       </c>
       <c r="C17" t="n">
-        <v>73.00841174603173</v>
-      </c>
-      <c r="D17" t="n">
-        <v>72.23012496031744</v>
+        <v>72.3102981215748</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +663,7 @@
         <v>2025</v>
       </c>
       <c r="C18" t="n">
-        <v>72.3660474801587</v>
-      </c>
-      <c r="D18" t="n">
-        <v>71.70115386904766</v>
+        <v>71.9824362800377</v>
       </c>
     </row>
     <row r="19">
@@ -732,10 +676,7 @@
         <v>2025</v>
       </c>
       <c r="C19" t="n">
-        <v>69.96922922161167</v>
-      </c>
-      <c r="D19" t="n">
-        <v>69.77425182720053</v>
+        <v>69.03176301046176</v>
       </c>
     </row>
     <row r="20">
@@ -748,10 +689,7 @@
         <v>2025</v>
       </c>
       <c r="C20" t="n">
-        <v>76.24578879731382</v>
-      </c>
-      <c r="D20" t="n">
-        <v>76.30262157661787</v>
+        <v>74.18386367526193</v>
       </c>
     </row>
     <row r="21">
@@ -764,10 +702,7 @@
         <v>2025</v>
       </c>
       <c r="C21" t="n">
-        <v>69.87332084184985</v>
-      </c>
-      <c r="D21" t="n">
-        <v>69.82985179012873</v>
+        <v>69.06548386612572</v>
       </c>
     </row>
     <row r="22">
@@ -780,10 +715,7 @@
         <v>2025</v>
       </c>
       <c r="C22" t="n">
-        <v>70.91499133297265</v>
-      </c>
-      <c r="D22" t="n">
-        <v>70.2746342992899</v>
+        <v>70.41332517472111</v>
       </c>
     </row>
     <row r="23">
@@ -796,10 +728,7 @@
         <v>2025</v>
       </c>
       <c r="C23" t="n">
-        <v>70.23505556913121</v>
-      </c>
-      <c r="D23" t="n">
-        <v>69.85044739376467</v>
+        <v>69.64642065515969</v>
       </c>
     </row>
     <row r="24">
@@ -812,10 +741,7 @@
         <v>2025</v>
       </c>
       <c r="C24" t="n">
-        <v>73.00384263888887</v>
-      </c>
-      <c r="D24" t="n">
-        <v>72.24650476190473</v>
+        <v>72.65953551971437</v>
       </c>
     </row>
     <row r="25">
@@ -828,10 +754,7 @@
         <v>2025</v>
       </c>
       <c r="C25" t="n">
-        <v>70.3436605104618</v>
-      </c>
-      <c r="D25" t="n">
-        <v>69.87667739775806</v>
+        <v>69.97097064014461</v>
       </c>
     </row>
     <row r="26">
@@ -844,10 +767,7 @@
         <v>2025</v>
       </c>
       <c r="C26" t="n">
-        <v>69.57516104653679</v>
-      </c>
-      <c r="D26" t="n">
-        <v>69.34763910894664</v>
+        <v>68.61086950985701</v>
       </c>
     </row>
     <row r="27">
@@ -860,10 +780,7 @@
         <v>2025</v>
       </c>
       <c r="C27" t="n">
-        <v>71.86359432539685</v>
-      </c>
-      <c r="D27" t="n">
-        <v>70.9211903012266</v>
+        <v>71.18723955347734</v>
       </c>
     </row>
     <row r="28">
@@ -876,10 +793,7 @@
         <v>2025</v>
       </c>
       <c r="C28" t="n">
-        <v>74.76698467809962</v>
-      </c>
-      <c r="D28" t="n">
-        <v>74.51587798701291</v>
+        <v>73.03331552757663</v>
       </c>
     </row>
     <row r="29">
@@ -892,10 +806,7 @@
         <v>2025</v>
       </c>
       <c r="C29" t="n">
-        <v>71.87154396825399</v>
-      </c>
-      <c r="D29" t="n">
-        <v>70.92422815836944</v>
+        <v>71.30136681210136</v>
       </c>
     </row>
     <row r="30">
@@ -908,10 +819,7 @@
         <v>2025</v>
       </c>
       <c r="C30" t="n">
-        <v>68.80912606782108</v>
-      </c>
-      <c r="D30" t="n">
-        <v>68.67129505591627</v>
+        <v>68.41742974927851</v>
       </c>
     </row>
     <row r="31">
@@ -924,10 +832,7 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>74.38166690566372</v>
-      </c>
-      <c r="D31" t="n">
-        <v>74.38604609217164</v>
+        <v>73.46350077476001</v>
       </c>
     </row>
     <row r="32">
@@ -940,10 +845,7 @@
         <v>2025</v>
       </c>
       <c r="C32" t="n">
-        <v>69.96380410256407</v>
-      </c>
-      <c r="D32" t="n">
-        <v>69.79870509620977</v>
+        <v>69.39165083998236</v>
       </c>
     </row>
     <row r="33">
@@ -956,10 +858,7 @@
         <v>2025</v>
       </c>
       <c r="C33" t="n">
-        <v>69.95911630494503</v>
-      </c>
-      <c r="D33" t="n">
-        <v>69.64170533910529</v>
+        <v>69.46432512085138</v>
       </c>
     </row>
     <row r="34">
@@ -972,10 +871,7 @@
         <v>2025</v>
       </c>
       <c r="C34" t="n">
-        <v>70.99946946428577</v>
-      </c>
-      <c r="D34" t="n">
-        <v>70.25772639524951</v>
+        <v>70.85578117851716</v>
       </c>
     </row>
     <row r="35">
@@ -988,10 +884,7 @@
         <v>2025</v>
       </c>
       <c r="C35" t="n">
-        <v>69.93313459859581</v>
-      </c>
-      <c r="D35" t="n">
-        <v>69.71034023529462</v>
+        <v>69.00643077460164</v>
       </c>
     </row>
     <row r="36">
@@ -1004,10 +897,7 @@
         <v>2025</v>
       </c>
       <c r="C36" t="n">
-        <v>71.40979787698419</v>
-      </c>
-      <c r="D36" t="n">
-        <v>70.57356456168831</v>
+        <v>71.1928753120617</v>
       </c>
     </row>
     <row r="37">
@@ -1020,10 +910,7 @@
         <v>2025</v>
       </c>
       <c r="C37" t="n">
-        <v>70.87067657106785</v>
-      </c>
-      <c r="D37" t="n">
-        <v>70.2289587635756</v>
+        <v>70.57137502003194</v>
       </c>
     </row>
     <row r="38">
@@ -1036,10 +923,7 @@
         <v>2025</v>
       </c>
       <c r="C38" t="n">
-        <v>70.333271144528</v>
-      </c>
-      <c r="D38" t="n">
-        <v>69.87321250692405</v>
+        <v>69.91184569559225</v>
       </c>
     </row>
     <row r="39">
@@ -1052,10 +936,7 @@
         <v>2025</v>
       </c>
       <c r="C39" t="n">
-        <v>70.5336675541126</v>
-      </c>
-      <c r="D39" t="n">
-        <v>69.96263849206349</v>
+        <v>70.30510514039896</v>
       </c>
     </row>
     <row r="40">
@@ -1068,10 +949,7 @@
         <v>2025</v>
       </c>
       <c r="C40" t="n">
-        <v>71.99397360224398</v>
-      </c>
-      <c r="D40" t="n">
-        <v>70.99060229617609</v>
+        <v>71.2284084164433</v>
       </c>
     </row>
     <row r="41">
@@ -1084,10 +962,7 @@
         <v>2025</v>
       </c>
       <c r="C41" t="n">
-        <v>70.18138142230579</v>
-      </c>
-      <c r="D41" t="n">
-        <v>69.72591703243124</v>
+        <v>69.69186295427525</v>
       </c>
     </row>
     <row r="42">
@@ -1100,10 +975,7 @@
         <v>2025</v>
       </c>
       <c r="C42" t="n">
-        <v>69.90624534181097</v>
-      </c>
-      <c r="D42" t="n">
-        <v>69.84249822601008</v>
+        <v>68.98481617286309</v>
       </c>
     </row>
     <row r="43">
@@ -1116,10 +988,7 @@
         <v>2025</v>
       </c>
       <c r="C43" t="n">
-        <v>69.83554622255784</v>
-      </c>
-      <c r="D43" t="n">
-        <v>69.79331524250965</v>
+        <v>68.86082809277464</v>
       </c>
     </row>
     <row r="44">
@@ -1132,10 +1001,7 @@
         <v>2025</v>
       </c>
       <c r="C44" t="n">
-        <v>75.39947589133078</v>
-      </c>
-      <c r="D44" t="n">
-        <v>75.40469124847364</v>
+        <v>73.44160831772697</v>
       </c>
     </row>
     <row r="45">
@@ -1148,10 +1014,7 @@
         <v>2025</v>
       </c>
       <c r="C45" t="n">
-        <v>68.9933350757576</v>
-      </c>
-      <c r="D45" t="n">
-        <v>68.70651573967699</v>
+        <v>68.39447627213789</v>
       </c>
     </row>
     <row r="46">
@@ -1164,10 +1027,7 @@
         <v>2025</v>
       </c>
       <c r="C46" t="n">
-        <v>72.62738982142857</v>
-      </c>
-      <c r="D46" t="n">
-        <v>72.13781418319083</v>
+        <v>72.29705348037425</v>
       </c>
     </row>
     <row r="47">
@@ -1180,10 +1040,7 @@
         <v>2025</v>
       </c>
       <c r="C47" t="n">
-        <v>69.29835877831107</v>
-      </c>
-      <c r="D47" t="n">
-        <v>68.75771569083695</v>
+        <v>68.57483815205632</v>
       </c>
     </row>
     <row r="48">
@@ -1196,10 +1053,7 @@
         <v>2025</v>
       </c>
       <c r="C48" t="n">
-        <v>78.30569299603171</v>
-      </c>
-      <c r="D48" t="n">
-        <v>77.86614144300138</v>
+        <v>75.92927964504064</v>
       </c>
     </row>
     <row r="49">
@@ -1212,10 +1066,7 @@
         <v>2025</v>
       </c>
       <c r="C49" t="n">
-        <v>78.47247692460316</v>
-      </c>
-      <c r="D49" t="n">
-        <v>77.99106084776332</v>
+        <v>76.03724468975473</v>
       </c>
     </row>
     <row r="50">
@@ -1228,10 +1079,7 @@
         <v>2025</v>
       </c>
       <c r="C50" t="n">
-        <v>74.39055444444442</v>
-      </c>
-      <c r="D50" t="n">
-        <v>74.36318464285709</v>
+        <v>72.71282946908885</v>
       </c>
     </row>
     <row r="51">
@@ -1244,10 +1092,7 @@
         <v>2025</v>
       </c>
       <c r="C51" t="n">
-        <v>69.48407611549875</v>
-      </c>
-      <c r="D51" t="n">
-        <v>69.12575218692734</v>
+        <v>68.52411491192383</v>
       </c>
     </row>
     <row r="52">
@@ -1260,10 +1105,7 @@
         <v>2025</v>
       </c>
       <c r="C52" t="n">
-        <v>69.96897201923073</v>
-      </c>
-      <c r="D52" t="n">
-        <v>69.76810174541082</v>
+        <v>69.16799495777099</v>
       </c>
     </row>
     <row r="53">
@@ -1276,10 +1118,7 @@
         <v>2025</v>
       </c>
       <c r="C53" t="n">
-        <v>72.01289339120504</v>
-      </c>
-      <c r="D53" t="n">
-        <v>71.04471855519488</v>
+        <v>71.42457682608875</v>
       </c>
     </row>
     <row r="54">
@@ -1292,10 +1131,7 @@
         <v>2025</v>
       </c>
       <c r="C54" t="n">
-        <v>70.95979224567104</v>
-      </c>
-      <c r="D54" t="n">
-        <v>70.25416180194807</v>
+        <v>71.06811312120364</v>
       </c>
     </row>
     <row r="55">
@@ -1308,10 +1144,7 @@
         <v>2025</v>
       </c>
       <c r="C55" t="n">
-        <v>73.29899968253966</v>
-      </c>
-      <c r="D55" t="n">
-        <v>72.58414547619046</v>
+        <v>72.52254629534065</v>
       </c>
     </row>
     <row r="56">
@@ -1324,10 +1157,7 @@
         <v>2025</v>
       </c>
       <c r="C56" t="n">
-        <v>67.27215010461757</v>
-      </c>
-      <c r="D56" t="n">
-        <v>67.60832706890329</v>
+        <v>67.81995208333328</v>
       </c>
     </row>
     <row r="57">
@@ -1340,10 +1170,7 @@
         <v>2025</v>
       </c>
       <c r="C57" t="n">
-        <v>76.05781855921855</v>
-      </c>
-      <c r="D57" t="n">
-        <v>76.25482711233212</v>
+        <v>73.81478351678551</v>
       </c>
     </row>
     <row r="58">
@@ -1356,10 +1183,7 @@
         <v>2025</v>
       </c>
       <c r="C58" t="n">
-        <v>74.67610972943714</v>
-      </c>
-      <c r="D58" t="n">
-        <v>74.45286584415578</v>
+        <v>73.70677281575006</v>
       </c>
     </row>
     <row r="59">
@@ -1372,10 +1196,7 @@
         <v>2025</v>
       </c>
       <c r="C59" t="n">
-        <v>66.80938938492062</v>
-      </c>
-      <c r="D59" t="n">
-        <v>66.8130793849206</v>
+        <v>67.69384484022558</v>
       </c>
     </row>
     <row r="60">
@@ -1388,10 +1209,7 @@
         <v>2025</v>
       </c>
       <c r="C60" t="n">
-        <v>70.0357409550172</v>
-      </c>
-      <c r="D60" t="n">
-        <v>69.90943861921455</v>
+        <v>69.32415156208079</v>
       </c>
     </row>
     <row r="61">
@@ -1404,10 +1222,7 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>72.67428055555553</v>
-      </c>
-      <c r="D61" t="n">
-        <v>72.14032326133488</v>
+        <v>72.31779839789145</v>
       </c>
     </row>
     <row r="62">
@@ -1420,10 +1235,7 @@
         <v>2025</v>
       </c>
       <c r="C62" t="n">
-        <v>72.59319849206349</v>
-      </c>
-      <c r="D62" t="n">
-        <v>72.10512054046099</v>
+        <v>71.76602370491969</v>
       </c>
     </row>
     <row r="63">
@@ -1436,10 +1248,7 @@
         <v>2025</v>
       </c>
       <c r="C63" t="n">
-        <v>71.96652597057013</v>
-      </c>
-      <c r="D63" t="n">
-        <v>71.02011728896109</v>
+        <v>71.40359447130079</v>
       </c>
     </row>
     <row r="64">
@@ -1452,10 +1261,7 @@
         <v>2025</v>
       </c>
       <c r="C64" t="n">
-        <v>72.6853581547619</v>
-      </c>
-      <c r="D64" t="n">
-        <v>72.1348613855718</v>
+        <v>72.01498281471542</v>
       </c>
     </row>
     <row r="65">
@@ -1468,10 +1274,7 @@
         <v>2025</v>
       </c>
       <c r="C65" t="n">
-        <v>69.83715970576596</v>
-      </c>
-      <c r="D65" t="n">
-        <v>69.75952822601009</v>
+        <v>69.25746439754687</v>
       </c>
     </row>
     <row r="66">
@@ -1484,10 +1287,7 @@
         <v>2025</v>
       </c>
       <c r="C66" t="n">
-        <v>70.85037538059166</v>
-      </c>
-      <c r="D66" t="n">
-        <v>70.21275078738513</v>
+        <v>71.11635565025834</v>
       </c>
     </row>
     <row r="67">
@@ -1500,10 +1300,7 @@
         <v>2025</v>
       </c>
       <c r="C67" t="n">
-        <v>70.52399041125547</v>
-      </c>
-      <c r="D67" t="n">
-        <v>69.94827218253967</v>
+        <v>70.13071135374113</v>
       </c>
     </row>
     <row r="68">
@@ -1516,10 +1313,7 @@
         <v>2025</v>
       </c>
       <c r="C68" t="n">
-        <v>74.85829465825837</v>
-      </c>
-      <c r="D68" t="n">
-        <v>74.6011018362193</v>
+        <v>73.16822556952442</v>
       </c>
     </row>
     <row r="69">
@@ -1532,10 +1326,7 @@
         <v>2025</v>
       </c>
       <c r="C69" t="n">
-        <v>72.02003355173893</v>
-      </c>
-      <c r="D69" t="n">
-        <v>70.98576974567105</v>
+        <v>71.26186444864338</v>
       </c>
     </row>
     <row r="70">
@@ -1548,10 +1339,7 @@
         <v>2025</v>
       </c>
       <c r="C70" t="n">
-        <v>69.98605899614273</v>
-      </c>
-      <c r="D70" t="n">
-        <v>69.74899194192486</v>
+        <v>69.41864695273536</v>
       </c>
     </row>
     <row r="71">
@@ -1564,10 +1352,7 @@
         <v>2025</v>
       </c>
       <c r="C71" t="n">
-        <v>72.30059724206347</v>
-      </c>
-      <c r="D71" t="n">
-        <v>71.62102247114001</v>
+        <v>71.81031088529036</v>
       </c>
     </row>
     <row r="72">
@@ -1580,10 +1365,7 @@
         <v>2025</v>
       </c>
       <c r="C72" t="n">
-        <v>71.35189353535357</v>
-      </c>
-      <c r="D72" t="n">
-        <v>70.54585668831167</v>
+        <v>70.96774681857151</v>
       </c>
     </row>
     <row r="73">
@@ -1596,10 +1378,7 @@
         <v>2025</v>
       </c>
       <c r="C73" t="n">
-        <v>75.51926762112876</v>
-      </c>
-      <c r="D73" t="n">
-        <v>75.56841815684304</v>
+        <v>73.55910202559251</v>
       </c>
     </row>
     <row r="74">
@@ -1612,10 +1391,7 @@
         <v>2025</v>
       </c>
       <c r="C74" t="n">
-        <v>71.63286970238099</v>
-      </c>
-      <c r="D74" t="n">
-        <v>70.69388798881675</v>
+        <v>71.23323892524766</v>
       </c>
     </row>
     <row r="75">
@@ -1628,10 +1404,7 @@
         <v>2025</v>
       </c>
       <c r="C75" t="n">
-        <v>70.93667387265518</v>
-      </c>
-      <c r="D75" t="n">
-        <v>70.3445290377459</v>
+        <v>70.98799503188052</v>
       </c>
     </row>
     <row r="76">
@@ -1644,10 +1417,7 @@
         <v>2025</v>
       </c>
       <c r="C76" t="n">
-        <v>69.85965619548011</v>
-      </c>
-      <c r="D76" t="n">
-        <v>69.79240632124818</v>
+        <v>69.2777678699246</v>
       </c>
     </row>
     <row r="77">
@@ -1660,10 +1430,7 @@
         <v>2025</v>
       </c>
       <c r="C77" t="n">
-        <v>76.32901453144081</v>
-      </c>
-      <c r="D77" t="n">
-        <v>76.38702237026865</v>
+        <v>74.04186633447803</v>
       </c>
     </row>
     <row r="78">
@@ -1676,10 +1443,7 @@
         <v>2025</v>
       </c>
       <c r="C78" t="n">
-        <v>71.8749766810967</v>
-      </c>
-      <c r="D78" t="n">
-        <v>70.96028886544015</v>
+        <v>72.42738969710845</v>
       </c>
     </row>
     <row r="79">
@@ -1692,10 +1456,7 @@
         <v>2025</v>
       </c>
       <c r="C79" t="n">
-        <v>76.20309568223445</v>
-      </c>
-      <c r="D79" t="n">
-        <v>76.44399306471313</v>
+        <v>74.73623119769121</v>
       </c>
     </row>
     <row r="80">
@@ -1708,10 +1469,7 @@
         <v>2025</v>
       </c>
       <c r="C80" t="n">
-        <v>72.31398700396824</v>
-      </c>
-      <c r="D80" t="n">
-        <v>71.63002021464651</v>
+        <v>71.93916418586801</v>
       </c>
     </row>
     <row r="81">
@@ -1724,10 +1482,7 @@
         <v>2025</v>
       </c>
       <c r="C81" t="n">
-        <v>65.7572507593795</v>
-      </c>
-      <c r="D81" t="n">
-        <v>65.65254819985569</v>
+        <v>65.70648320165948</v>
       </c>
     </row>
     <row r="82">
@@ -1740,10 +1495,7 @@
         <v>2025</v>
       </c>
       <c r="C82" t="n">
-        <v>74.82667265873006</v>
-      </c>
-      <c r="D82" t="n">
-        <v>74.51313151875897</v>
+        <v>73.50567067962234</v>
       </c>
     </row>
     <row r="83">
@@ -1756,10 +1508,7 @@
         <v>2025</v>
       </c>
       <c r="C83" t="n">
-        <v>70.94265561868693</v>
-      </c>
-      <c r="D83" t="n">
-        <v>70.3139803508772</v>
+        <v>70.59263211827047</v>
       </c>
     </row>
     <row r="84">
@@ -1772,10 +1521,7 @@
         <v>2025</v>
       </c>
       <c r="C84" t="n">
-        <v>78.2284050396825</v>
-      </c>
-      <c r="D84" t="n">
-        <v>77.7958305104617</v>
+        <v>75.95186679716119</v>
       </c>
     </row>
     <row r="85">
@@ -1788,10 +1534,7 @@
         <v>2025</v>
       </c>
       <c r="C85" t="n">
-        <v>76.49568935078813</v>
-      </c>
-      <c r="D85" t="n">
-        <v>76.54419351745479</v>
+        <v>74.80454191350317</v>
       </c>
     </row>
     <row r="86">
@@ -1804,10 +1547,7 @@
         <v>2025</v>
       </c>
       <c r="C86" t="n">
-        <v>76.02851451159952</v>
-      </c>
-      <c r="D86" t="n">
-        <v>76.2348195131258</v>
+        <v>73.89427926339962</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/Random Forest/predictions_ele_2025.xlsx
+++ b/notebooks/Random Forest/predictions_ele_2025.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ОПЖ_прогноз</t>
+          <t>predictions</t>
         </is>
       </c>
     </row>
@@ -468,7 +468,7 @@
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>67.88796251984124</v>
+        <v>67.88796251984122</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>70.15226491526761</v>
+        <v>70.15226491526762</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>71.23793286160405</v>
+        <v>71.23793286160408</v>
       </c>
     </row>
     <row r="6">
@@ -520,7 +520,7 @@
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>70.64335969244267</v>
+        <v>70.64335969244269</v>
       </c>
     </row>
     <row r="8">
@@ -546,7 +546,7 @@
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>72.19887734028204</v>
+        <v>72.19887734028202</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>70.48455934072689</v>
+        <v>70.4845593407269</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>71.53173902849305</v>
+        <v>71.53173902849306</v>
       </c>
     </row>
     <row r="12">
@@ -637,7 +637,7 @@
         <v>2025</v>
       </c>
       <c r="C16" t="n">
-        <v>74.70453910466946</v>
+        <v>74.70453910466948</v>
       </c>
     </row>
     <row r="17">
@@ -650,7 +650,7 @@
         <v>2025</v>
       </c>
       <c r="C17" t="n">
-        <v>72.3102981215748</v>
+        <v>72.31029812157482</v>
       </c>
     </row>
     <row r="18">
@@ -676,7 +676,7 @@
         <v>2025</v>
       </c>
       <c r="C19" t="n">
-        <v>69.03176301046176</v>
+        <v>69.03176301046177</v>
       </c>
     </row>
     <row r="20">
@@ -689,7 +689,7 @@
         <v>2025</v>
       </c>
       <c r="C20" t="n">
-        <v>74.18386367526193</v>
+        <v>74.1838636752619</v>
       </c>
     </row>
     <row r="21">
@@ -702,7 +702,7 @@
         <v>2025</v>
       </c>
       <c r="C21" t="n">
-        <v>69.06548386612572</v>
+        <v>69.06548386612573</v>
       </c>
     </row>
     <row r="22">
@@ -728,7 +728,7 @@
         <v>2025</v>
       </c>
       <c r="C23" t="n">
-        <v>69.64642065515969</v>
+        <v>69.6464206551597</v>
       </c>
     </row>
     <row r="24">
@@ -741,7 +741,7 @@
         <v>2025</v>
       </c>
       <c r="C24" t="n">
-        <v>72.65953551971437</v>
+        <v>72.6595355197144</v>
       </c>
     </row>
     <row r="25">
@@ -754,7 +754,7 @@
         <v>2025</v>
       </c>
       <c r="C25" t="n">
-        <v>69.97097064014461</v>
+        <v>69.97097064014464</v>
       </c>
     </row>
     <row r="26">
@@ -780,7 +780,7 @@
         <v>2025</v>
       </c>
       <c r="C27" t="n">
-        <v>71.18723955347734</v>
+        <v>71.18723955347735</v>
       </c>
     </row>
     <row r="28">
@@ -793,7 +793,7 @@
         <v>2025</v>
       </c>
       <c r="C28" t="n">
-        <v>73.03331552757663</v>
+        <v>73.03331552757665</v>
       </c>
     </row>
     <row r="29">
@@ -806,7 +806,7 @@
         <v>2025</v>
       </c>
       <c r="C29" t="n">
-        <v>71.30136681210136</v>
+        <v>71.30136681210139</v>
       </c>
     </row>
     <row r="30">
@@ -819,7 +819,7 @@
         <v>2025</v>
       </c>
       <c r="C30" t="n">
-        <v>68.41742974927851</v>
+        <v>68.41742974927853</v>
       </c>
     </row>
     <row r="31">
@@ -845,7 +845,7 @@
         <v>2025</v>
       </c>
       <c r="C32" t="n">
-        <v>69.39165083998236</v>
+        <v>69.39165083998238</v>
       </c>
     </row>
     <row r="33">
@@ -858,7 +858,7 @@
         <v>2025</v>
       </c>
       <c r="C33" t="n">
-        <v>69.46432512085138</v>
+        <v>69.46432512085141</v>
       </c>
     </row>
     <row r="34">
@@ -871,7 +871,7 @@
         <v>2025</v>
       </c>
       <c r="C34" t="n">
-        <v>70.85578117851716</v>
+        <v>70.85578117851718</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         <v>2025</v>
       </c>
       <c r="C35" t="n">
-        <v>69.00643077460164</v>
+        <v>69.00643077460165</v>
       </c>
     </row>
     <row r="36">
@@ -897,7 +897,7 @@
         <v>2025</v>
       </c>
       <c r="C36" t="n">
-        <v>71.1928753120617</v>
+        <v>71.19287531206173</v>
       </c>
     </row>
     <row r="37">
@@ -910,7 +910,7 @@
         <v>2025</v>
       </c>
       <c r="C37" t="n">
-        <v>70.57137502003194</v>
+        <v>70.57137502003195</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         <v>2025</v>
       </c>
       <c r="C38" t="n">
-        <v>69.91184569559225</v>
+        <v>69.91184569559223</v>
       </c>
     </row>
     <row r="39">
@@ -936,7 +936,7 @@
         <v>2025</v>
       </c>
       <c r="C39" t="n">
-        <v>70.30510514039896</v>
+        <v>70.30510514039898</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         <v>2025</v>
       </c>
       <c r="C40" t="n">
-        <v>71.2284084164433</v>
+        <v>71.22840841644334</v>
       </c>
     </row>
     <row r="41">
@@ -962,7 +962,7 @@
         <v>2025</v>
       </c>
       <c r="C41" t="n">
-        <v>69.69186295427525</v>
+        <v>69.69186295427527</v>
       </c>
     </row>
     <row r="42">
@@ -1001,7 +1001,7 @@
         <v>2025</v>
       </c>
       <c r="C44" t="n">
-        <v>73.44160831772697</v>
+        <v>73.44160831772696</v>
       </c>
     </row>
     <row r="45">
@@ -1040,7 +1040,7 @@
         <v>2025</v>
       </c>
       <c r="C47" t="n">
-        <v>68.57483815205632</v>
+        <v>68.5748381520563</v>
       </c>
     </row>
     <row r="48">
@@ -1053,7 +1053,7 @@
         <v>2025</v>
       </c>
       <c r="C48" t="n">
-        <v>75.92927964504064</v>
+        <v>75.92927964504065</v>
       </c>
     </row>
     <row r="49">
@@ -1066,7 +1066,7 @@
         <v>2025</v>
       </c>
       <c r="C49" t="n">
-        <v>76.03724468975473</v>
+        <v>76.03724468975474</v>
       </c>
     </row>
     <row r="50">
@@ -1079,7 +1079,7 @@
         <v>2025</v>
       </c>
       <c r="C50" t="n">
-        <v>72.71282946908885</v>
+        <v>72.71282946908883</v>
       </c>
     </row>
     <row r="51">
@@ -1118,7 +1118,7 @@
         <v>2025</v>
       </c>
       <c r="C53" t="n">
-        <v>71.42457682608875</v>
+        <v>71.42457682608878</v>
       </c>
     </row>
     <row r="54">
@@ -1157,7 +1157,7 @@
         <v>2025</v>
       </c>
       <c r="C56" t="n">
-        <v>67.81995208333328</v>
+        <v>67.81995208333329</v>
       </c>
     </row>
     <row r="57">
@@ -1170,7 +1170,7 @@
         <v>2025</v>
       </c>
       <c r="C57" t="n">
-        <v>73.81478351678551</v>
+        <v>73.8147835167855</v>
       </c>
     </row>
     <row r="58">
@@ -1183,7 +1183,7 @@
         <v>2025</v>
       </c>
       <c r="C58" t="n">
-        <v>73.70677281575006</v>
+        <v>73.70677281575007</v>
       </c>
     </row>
     <row r="59">
@@ -1209,7 +1209,7 @@
         <v>2025</v>
       </c>
       <c r="C60" t="n">
-        <v>69.32415156208079</v>
+        <v>69.32415156208077</v>
       </c>
     </row>
     <row r="61">
@@ -1248,7 +1248,7 @@
         <v>2025</v>
       </c>
       <c r="C63" t="n">
-        <v>71.40359447130079</v>
+        <v>71.40359447130081</v>
       </c>
     </row>
     <row r="64">
@@ -1274,7 +1274,7 @@
         <v>2025</v>
       </c>
       <c r="C65" t="n">
-        <v>69.25746439754687</v>
+        <v>69.2574643975469</v>
       </c>
     </row>
     <row r="66">
@@ -1326,7 +1326,7 @@
         <v>2025</v>
       </c>
       <c r="C69" t="n">
-        <v>71.26186444864338</v>
+        <v>71.26186444864341</v>
       </c>
     </row>
     <row r="70">
@@ -1352,7 +1352,7 @@
         <v>2025</v>
       </c>
       <c r="C71" t="n">
-        <v>71.81031088529036</v>
+        <v>71.81031088529038</v>
       </c>
     </row>
     <row r="72">
@@ -1365,7 +1365,7 @@
         <v>2025</v>
       </c>
       <c r="C72" t="n">
-        <v>70.96774681857151</v>
+        <v>70.96774681857154</v>
       </c>
     </row>
     <row r="73">
@@ -1378,7 +1378,7 @@
         <v>2025</v>
       </c>
       <c r="C73" t="n">
-        <v>73.55910202559251</v>
+        <v>73.55910202559249</v>
       </c>
     </row>
     <row r="74">
@@ -1391,7 +1391,7 @@
         <v>2025</v>
       </c>
       <c r="C74" t="n">
-        <v>71.23323892524766</v>
+        <v>71.23323892524769</v>
       </c>
     </row>
     <row r="75">
@@ -1404,7 +1404,7 @@
         <v>2025</v>
       </c>
       <c r="C75" t="n">
-        <v>70.98799503188052</v>
+        <v>70.98799503188054</v>
       </c>
     </row>
     <row r="76">
@@ -1443,7 +1443,7 @@
         <v>2025</v>
       </c>
       <c r="C78" t="n">
-        <v>72.42738969710845</v>
+        <v>72.42738969710847</v>
       </c>
     </row>
     <row r="79">
@@ -1482,7 +1482,7 @@
         <v>2025</v>
       </c>
       <c r="C81" t="n">
-        <v>65.70648320165948</v>
+        <v>65.70648320165951</v>
       </c>
     </row>
     <row r="82">
@@ -1495,7 +1495,7 @@
         <v>2025</v>
       </c>
       <c r="C82" t="n">
-        <v>73.50567067962234</v>
+        <v>73.50567067962231</v>
       </c>
     </row>
     <row r="83">
@@ -1508,7 +1508,7 @@
         <v>2025</v>
       </c>
       <c r="C83" t="n">
-        <v>70.59263211827047</v>
+        <v>70.5926321182705</v>
       </c>
     </row>
     <row r="84">
@@ -1534,7 +1534,7 @@
         <v>2025</v>
       </c>
       <c r="C85" t="n">
-        <v>74.80454191350317</v>
+        <v>74.80454191350319</v>
       </c>
     </row>
     <row r="86">
